--- a/data/data_processed/sources_table.xlsx
+++ b/data/data_processed/sources_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,61 +384,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Effectifs d'étudiants étrangers dans les établissements et les formations de l'enseignement supérieur</t>
+          <t>Liste des pays et territoires</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fr_effectifs_etudiants_etrangers_france</t>
+          <t>liste_pays</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>api_download</t>
+          <t>local_csv</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>data/data_raw/curiexplore-pays.csv</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.data.gouv.fr/api/1/datasets/r/7dfbef75-4fd8-464c-875d-38c4e067969b</t>
+          <t>https://data.enseignementsup-recherche.gouv.fr/explore/assets/curiexplore-pays/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Effectifs d'étudiants inscrits dans les établissements et les formations de l'enseignement supérieur</t>
+          <t>Effectifs d'étudiants étrangers dans les établissements et les formations de l'enseignement supérieur</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fr_effectifs_etab</t>
+          <t>fr_effectifs_etudiants_etrangers_france</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>local_csv</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>data/data_raw/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables.csv</t>
+          <t>api_download</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://data.enseignementsup-recherche.gouv.fr/explore/dataset/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables/information/?disjunctive.rgp_formations_ou_etablissements</t>
+          <t>https://www.data.gouv.fr/api/1/datasets/r/7dfbef75-4fd8-464c-875d-38c4e067969b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nouveaux inscrits doctorat</t>
+          <t>Effectifs d'étudiants inscrits dans les établissements et les formations de l'enseignement supérieur</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fr_doctorat_etranger</t>
+          <t>fr_effectifs_etab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -448,24 +448,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>data/data_raw/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger.csv</t>
+          <t>data/data_raw/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables.csv</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://data.enseignementsup-recherche.gouv.fr/explore/assets/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger/</t>
+          <t>https://data.enseignementsup-recherche.gouv.fr/explore/dataset/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables/information/?disjunctive.rgp_formations_ou_etablissements</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HESA UK</t>
+          <t>Nouveaux inscrits doctorat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uk_hesa_all</t>
+          <t>fr_doctorat_etranger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -475,46 +475,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>data/data_raw/hesa_uk_data/table-1-202*-**.csv</t>
+          <t>data/data_raw/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger.csv</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.hesa.ac.uk/data-and-analysis/students/table-1</t>
+          <t>https://data.enseignementsup-recherche.gouv.fr/explore/assets/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_enrt01</t>
+          <t>HESA UK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eu_type_institution</t>
+          <t>uk_hesa_all</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eurostat_api</t>
+          <t>local_csv</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>data/data_raw/hesa_uk_data/table-1-202*-**.csv</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_enrt01/default/table?lang=en</t>
+          <t>https://www.hesa.ac.uk/data-and-analysis/students/table-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_mobs02</t>
+          <t>Eurostat educ_uoe_enrt01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eu_mobility_prev_diploma</t>
+          <t>eu_type_institution</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -524,19 +529,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs02/default/table?lang=en</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_enrt01/default/table?lang=en</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_mobs01</t>
+          <t>Eurostat educ_uoe_mobs02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eu_mobility_citizenship</t>
+          <t>eu_mobility_prev_diploma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -546,32 +551,54 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs01/default/table?lang=en</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs02/default/table?lang=en</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Eurostat educ_uoe_mobs01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>eu_mobility_citizenship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eurostat_api</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs01/default/table?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>UNESCO data (outbound and inbound students, outbound mobility ratio, inbound mobility rate)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>unesco</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>local_csv</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>data/data_raw/unesco/data.csv</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://databrowser.uis.unesco.org/browser/EDUCATION/UIS-EducationOPRI/int-stud</t>
         </is>

--- a/data/data_processed/sources_table.xlsx
+++ b/data/data_processed/sources_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -433,12 +433,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Effectifs d'étudiants inscrits dans les établissements et les formations de l'enseignement supérieur</t>
+          <t>Effectifs d'étudiants inscrits dans les établissements publics sous tutelle du ministère en charge de l’Enseignement supérieur</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fr_effectifs_etab</t>
+          <t>fr_effectifs_etablissement_202*</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -448,24 +448,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>data/data_raw/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables.csv</t>
+          <t>data/data_raw/fr-esr-sise-effectifs-d-etudiants-inscrits-esr-public/fr-esr-sise-effectifs-d-etudiants-inscrits-esr-public_202*_202*.csv</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://data.enseignementsup-recherche.gouv.fr/explore/dataset/fr-esr-atlas_regional-effectifs-d-etudiants-inscrits_agregeables/information/?disjunctive.rgp_formations_ou_etablissements</t>
+          <t>https://data.enseignementsup-recherche.gouv.fr/explore/dataset/fr-esr-sise-effectifs-d-etudiants-inscrits-esr-public/?tab=metas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nouveaux inscrits doctorat</t>
+          <t>HESA UK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fr_doctorat_etranger</t>
+          <t>uk_hesa_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -475,51 +475,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>data/data_raw/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger.csv</t>
+          <t>data/data_raw/hesa_uk_data/table-1-202*-**.csv</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://data.enseignementsup-recherche.gouv.fr/explore/assets/fr-esr-nouveaux-inscrits-doctorat-diplome-de-plus-haut-niveau-france-etranger/</t>
+          <t>https://www.hesa.ac.uk/data-and-analysis/students/table-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HESA UK</t>
+          <t>Eurostat educ_uoe_enrt01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>uk_hesa_all</t>
+          <t>eu_type_institution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>local_csv</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>data/data_raw/hesa_uk_data/table-1-202*-**.csv</t>
+          <t>eurostat_api</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.hesa.ac.uk/data-and-analysis/students/table-1</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_enrt01/default/table?lang=en</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_enrt01</t>
+          <t>Eurostat educ_uoe_mobs02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eu_type_institution</t>
+          <t>eu_mobility_prev_diploma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -529,19 +524,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_enrt01/default/table?lang=en</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs02/default/table?lang=en</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_mobs02</t>
+          <t>Eurostat educ_uoe_mobs01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eu_mobility_prev_diploma</t>
+          <t>eu_mobility_citizenship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -551,54 +546,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs02/default/table?lang=en</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs01/default/table?lang=en</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eurostat educ_uoe_mobs01</t>
+          <t>UNESCO data (outbound and inbound students, outbound mobility ratio, inbound mobility rate)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eu_mobility_citizenship</t>
+          <t>unesco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eurostat_api</t>
+          <t>local_csv</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>data/data_raw/unesco/data.csv</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/educ_uoe_mobs01/default/table?lang=en</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UNESCO data (outbound and inbound students, outbound mobility ratio, inbound mobility rate)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>unesco</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>local_csv</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>data/data_raw/unesco/data.csv</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>https://databrowser.uis.unesco.org/browser/EDUCATION/UIS-EducationOPRI/int-stud</t>
         </is>
